--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_5_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_5_inference.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Pg Vm Model False</t>
   </si>
@@ -31,82 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
     <t>qg_tot</t>
   </si>
   <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
     <t>nn_input</t>
   </si>
   <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
-    <t>0.52 (1.34)</t>
-  </si>
-  <si>
-    <t>65342.32 (67523.48 &gt; 3.22%)</t>
-  </si>
-  <si>
-    <t>0.58 (1.34)</t>
-  </si>
-  <si>
-    <t>65401.91 (67523.48 &gt; 3.13%)</t>
-  </si>
-  <si>
-    <t>-0.81 (1.34)</t>
-  </si>
-  <si>
-    <t>67809.59 (67523.48 &gt; 0.92%)</t>
-  </si>
-  <si>
-    <t>-0.78 (1.34)</t>
-  </si>
-  <si>
-    <t>67195.24 (67523.48 &gt; 0.79%)</t>
+    <t>65386.91 (67523.48 &gt; 3.16%)</t>
+  </si>
+  <si>
+    <t>0.55 (133.88)</t>
+  </si>
+  <si>
+    <t>65425.48 (67523.48 &gt; 3.11%)</t>
+  </si>
+  <si>
+    <t>0.57 (133.88)</t>
+  </si>
+  <si>
+    <t>67809.59 (67523.48 &gt; 0.42%)</t>
+  </si>
+  <si>
+    <t>-0.81 (133.88)</t>
+  </si>
+  <si>
+    <t>67195.23 (67523.48 &gt; 0.49%)</t>
+  </si>
+  <si>
+    <t>-0.78 (133.88)</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -488,34 +491,22 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0.1248771250247955</v>
-      </c>
-      <c r="C2">
-        <v>0.1248771250247955</v>
-      </c>
-      <c r="D2">
-        <v>0.08461768180131912</v>
-      </c>
-      <c r="E2">
-        <v>0.1146279498934746</v>
-      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.7114669680595398</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.7114804983139038</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0.0001296999398618937</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.0002210730744991452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -523,33 +514,33 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.074892014477066</v>
+        <v>9.826706886291504</v>
       </c>
       <c r="C4">
-        <v>1.074963168849664</v>
+        <v>9.82692813873291</v>
       </c>
       <c r="D4">
-        <v>0.03544490411877632</v>
+        <v>0.05112889781594276</v>
       </c>
       <c r="E4">
-        <v>0.03940698131918907</v>
+        <v>0.04792504757642746</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
+      <c r="B5">
+        <v>1.023407732985502</v>
+      </c>
+      <c r="C5">
+        <v>1.023431336341736</v>
+      </c>
+      <c r="D5">
+        <v>0.03708807751536369</v>
+      </c>
+      <c r="E5">
+        <v>0.04123590141534805</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,16 +548,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.002432885114103556</v>
+        <v>10.32344908901598</v>
       </c>
       <c r="C6">
-        <v>0.00243290513753891</v>
+        <v>10.32369225523958</v>
       </c>
       <c r="D6">
-        <v>3.469433067948557E-05</v>
+        <v>0.04912368580698967</v>
       </c>
       <c r="E6">
-        <v>0.0003166808455716819</v>
+        <v>0.04402065649628639</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -574,16 +565,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.5911921858787537</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5912097096443176</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3.219264181097969E-05</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.0003085106727667153</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -591,16 +582,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.5911679863929749</v>
+        <v>1.085022285532771</v>
       </c>
       <c r="C8">
-        <v>0.5912088751792908</v>
+        <v>1.085056849975735</v>
       </c>
       <c r="D8">
-        <v>3.219260179321282E-05</v>
+        <v>0.11118233948946</v>
       </c>
       <c r="E8">
-        <v>0.0003085111966356635</v>
+        <v>0.1239981204271317</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -608,16 +599,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.0002182420648407585</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.0003670157528967036</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.07240834087133408</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.06793113797903061</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -625,16 +616,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>2.946023591375392</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.946131689236498</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.0163023192435503</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.01413777284324169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -642,16 +633,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.023362773439488</v>
+        <v>2.946073083111932</v>
       </c>
       <c r="C11">
-        <v>1.02343034114937</v>
+        <v>2.946123319563084</v>
       </c>
       <c r="D11">
-        <v>0.03708319365978241</v>
+        <v>0.01630212739109993</v>
       </c>
       <c r="E11">
-        <v>0.04123057797551155</v>
+        <v>0.01413767784833908</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -659,16 +650,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1.074928481658358</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1.07495317410311</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.0354505330324173</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.03941293433308601</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -676,33 +667,33 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>1.202305316925049</v>
+        <v>0.7114707231521606</v>
       </c>
       <c r="C13">
-        <v>1.202409505844116</v>
+        <v>0.7114791870117188</v>
       </c>
       <c r="D13">
-        <v>0.1118401885032654</v>
+        <v>0.0001297004637308419</v>
       </c>
       <c r="E13">
-        <v>0.1243848130106926</v>
+        <v>0.0002210753009421751</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14">
-        <v>10.32322356822391</v>
-      </c>
-      <c r="C14">
-        <v>10.32373479195016</v>
-      </c>
-      <c r="D14">
-        <v>0.04912412539124489</v>
-      </c>
-      <c r="E14">
-        <v>0.04402095824480057</v>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,16 +701,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>9.826504707336426</v>
+        <v>1.202355980873108</v>
       </c>
       <c r="C15">
-        <v>9.82696533203125</v>
+        <v>1.202395915985107</v>
       </c>
       <c r="D15">
-        <v>0.05112912133336067</v>
+        <v>0.1118490695953369</v>
       </c>
       <c r="E15">
-        <v>0.04792517796158791</v>
+        <v>0.1243949756026268</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -727,16 +718,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -744,16 +735,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.0002500448143868262</v>
+        <v>0.124883659183979</v>
       </c>
       <c r="C17">
-        <v>0.0003956366406032856</v>
+        <v>0.124883659183979</v>
       </c>
       <c r="D17">
-        <v>0.07240856438875198</v>
+        <v>0.08463554829359055</v>
       </c>
       <c r="E17">
-        <v>0.06793136894702911</v>
+        <v>0.1146488040685654</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -761,16 +752,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1.084982963727858</v>
+        <v>0.002432880224660039</v>
       </c>
       <c r="C18">
-        <v>1.085061624486108</v>
+        <v>0.002432891400530934</v>
       </c>
       <c r="D18">
-        <v>0.1111734583973885</v>
+        <v>3.469414150458761E-05</v>
       </c>
       <c r="E18">
-        <v>0.1239879056811333</v>
+        <v>0.0003166803508065641</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -778,16 +769,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>3.154493479466111</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>3.154609622735785</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.01717578805983067</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.01505845692008734</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>3.154532541481835</v>
+      </c>
+      <c r="C20">
+        <v>3.154587756199793</v>
+      </c>
+      <c r="D20">
+        <v>0.01717561855912209</v>
+      </c>
+      <c r="E20">
+        <v>0.0150582529604435</v>
       </c>
     </row>
   </sheetData>
